--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_282_R29.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_282_R29.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4651</v>
+        <v>5.3122</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5389</v>
+        <v>5.9491</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.0738</v>
+        <v>-0.6369</v>
       </c>
       <c r="G2" t="n">
         <v>4.4645</v>
@@ -610,13 +610,13 @@
         <v>2.0876</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2983</v>
+        <v>-0.4512</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8259</v>
+        <v>0.2361</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.1242</v>
+        <v>-0.6873</v>
       </c>
       <c r="V2" t="n">
         <v>-0.7886</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. DIARRA</t>
+          <t>M. DIOUF</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7301</v>
+        <v>3.1755</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1032</v>
+        <v>2.4525</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6269</v>
+        <v>0.7229</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9883</v>
+        <v>1.2039</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5064</v>
+        <v>1.9399</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4819</v>
+        <v>-0.736</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0243</v>
+        <v>2.4834</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4354</v>
+        <v>2.373</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5889</v>
+        <v>0.1104</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.036</v>
+        <v>-1.2795</v>
       </c>
       <c r="N3" t="n">
-        <v>0.07099999999999999</v>
+        <v>-0.4331</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.107</v>
+        <v>-0.8464</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3917</v>
+        <v>2.7834</v>
       </c>
       <c r="S3" t="n">
-        <v>3.5847</v>
+        <v>0.3479</v>
       </c>
       <c r="T3" t="n">
-        <v>2.7052</v>
+        <v>0.9871</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8794999999999999</v>
+        <v>-0.6392</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.0026</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3943</v>
+        <v>0.1418</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.6083</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. DIOUF</t>
+          <t>A. DIARRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2192</v>
+        <v>2.4231</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1602</v>
+        <v>2.3339</v>
       </c>
       <c r="F4" t="n">
-        <v>1.059</v>
+        <v>0.0892</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2039</v>
+        <v>1.9883</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9399</v>
+        <v>1.5064</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.736</v>
+        <v>0.4819</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4834</v>
+        <v>2.0243</v>
       </c>
       <c r="K4" t="n">
-        <v>2.373</v>
+        <v>1.4354</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1104</v>
+        <v>0.5889</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2795</v>
+        <v>-0.036</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4331</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8464</v>
+        <v>-0.107</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7834</v>
+        <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3917</v>
+        <v>1.2777</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6948</v>
+        <v>0.9359</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3031</v>
+        <v>0.3418</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-2.0026</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1418</v>
+        <v>-0.3943</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1418</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8935999999999999</v>
+        <v>2.0395</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3077</v>
+        <v>2.4872</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4141</v>
+        <v>-0.4477</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4391</v>
@@ -844,13 +844,13 @@
         <v>2.0876</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.5951</v>
+        <v>-0.4492</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8057</v>
+        <v>0.3738</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7894</v>
+        <v>-0.823</v>
       </c>
       <c r="V5" t="n">
         <v>1.0722</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. NIANG</t>
+          <t>D. ALSTON JR.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0613</v>
+        <v>0.4217</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7236</v>
+        <v>-1.0725</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.6622</v>
+        <v>1.4942</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7362</v>
+        <v>-0.9179</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1909</v>
+        <v>1.1465</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5453</v>
+        <v>-2.0645</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8973</v>
+        <v>0.0438</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8605</v>
+        <v>1.5797</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0368</v>
+        <v>-1.5359</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6335</v>
+        <v>-0.9617</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0514</v>
+        <v>-0.4331</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5821</v>
+        <v>-0.5286</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6959</v>
+        <v>3.0154</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8877</v>
+        <v>-0.516</v>
       </c>
       <c r="T6" t="n">
-        <v>2.0761</v>
+        <v>0.0435</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1885</v>
+        <v>-0.5594</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. ALSTON JR.</t>
+          <t>L. VILDOZA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3868</v>
+        <v>-0.3549</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7802</v>
+        <v>0.426</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3934</v>
+        <v>-0.7809</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9179</v>
+        <v>1.5734</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1465</v>
+        <v>3.3467</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.0645</v>
+        <v>-1.7733</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0438</v>
+        <v>4.0505</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5797</v>
+        <v>4.1375</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.5359</v>
+        <v>-0.0871</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9617</v>
+        <v>-2.477</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4331</v>
+        <v>-0.7907999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5286</v>
+        <v>-1.6862</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8556</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1598</v>
+        <v>-3.7112</v>
       </c>
       <c r="R7" t="n">
-        <v>3.0154</v>
+        <v>2.5515</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3245</v>
+        <v>-0.7685999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6642</v>
+        <v>0.0868</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6603</v>
+        <v>-0.8552999999999999</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. AKELE</t>
+          <t>S. NIANG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.232</v>
+        <v>-1.0174</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5279</v>
+        <v>0.544</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2959</v>
+        <v>-1.5614</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3146</v>
+        <v>-0.7362</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6855</v>
+        <v>-0.1909</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6291</v>
+        <v>-0.5453</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3038</v>
+        <v>0.8973</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5175</v>
+        <v>0.8605</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7863</v>
+        <v>0.0368</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0108</v>
+        <v>-1.6335</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.168</v>
+        <v>-1.0514</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1573</v>
+        <v>-0.5821</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4639</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3813</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.224</v>
+        <v>0.8966</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1573</v>
+        <v>-0.0876</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. VILDOZA</t>
+          <t>K. JALLOW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5166</v>
+        <v>-1.1068</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3997</v>
+        <v>-0.54</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.117</v>
+        <v>-0.5668</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5734</v>
+        <v>-1.5481</v>
       </c>
       <c r="H9" t="n">
-        <v>3.3467</v>
+        <v>0.5498</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.7733</v>
+        <v>-2.0979</v>
       </c>
       <c r="J9" t="n">
-        <v>4.0505</v>
+        <v>-0.5009</v>
       </c>
       <c r="K9" t="n">
-        <v>4.1375</v>
+        <v>0.9614</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0871</v>
+        <v>-1.4623</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.477</v>
+        <v>-1.0472</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-0.4116</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6862</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.7112</v>
+        <v>-0.232</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5515</v>
+        <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.9303</v>
+        <v>-0.2546</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7389</v>
+        <v>0.1928</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.1914</v>
+        <v>-0.4474</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. JALLOW</t>
+          <t>N. AKELE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9825</v>
+        <v>-1.232</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2477</v>
+        <v>-1.5279</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7348</v>
+        <v>0.2959</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5481</v>
+        <v>-1.3146</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5498</v>
+        <v>-0.6855</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.0979</v>
+        <v>-0.6291</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5009</v>
+        <v>-1.3038</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9614</v>
+        <v>-0.5175</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4623</v>
+        <v>-0.7863</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0472</v>
+        <v>-0.0108</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4116</v>
+        <v>-0.168</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6356000000000001</v>
+        <v>0.1573</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1303</v>
+        <v>-0.3813</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5149</v>
+        <v>-0.224</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6155</v>
+        <v>-0.1573</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.3252</v>
+        <v>-5.7348</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.2094</v>
+        <v>-6.3838</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8842</v>
+        <v>0.649</v>
       </c>
       <c r="G11" t="n">
         <v>-4.4463</v>
@@ -1312,13 +1312,13 @@
         <v>2.5515</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9510999999999999</v>
+        <v>-0.3607</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8136</v>
+        <v>0.0121</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1375</v>
+        <v>-0.3727</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.926200000000001</v>
+        <v>3.926100000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>4.6687</v>
+        <v>4.668499999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7425</v>
+        <v>-0.7424999999999997</v>
       </c>
       <c r="G12" t="n">
         <v>-0.1720999999999995</v>
@@ -1363,7 +1363,7 @@
         <v>-11.0416</v>
       </c>
       <c r="J12" t="n">
-        <v>9.872300000000001</v>
+        <v>9.872299999999999</v>
       </c>
       <c r="K12" t="n">
         <v>15.0927</v>
@@ -1390,13 +1390,13 @@
         <v>18.5563</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7467999999999998</v>
+        <v>-0.7469999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>3.5407</v>
+        <v>3.540699999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.2877</v>
+        <v>-4.2874</v>
       </c>
       <c r="V12" t="n">
         <v>-2.1133</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.557</v>
+        <v>5.6636</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9093</v>
+        <v>6.7349</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3523</v>
+        <v>-1.0714</v>
       </c>
       <c r="G13" t="n">
         <v>4.5284</v>
@@ -1468,13 +1468,13 @@
         <v>1.6237</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5951</v>
+        <v>-0.4885</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7468</v>
+        <v>0.0788</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8483000000000001</v>
+        <v>-0.5673</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7137</v>
+        <v>3.3497</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0506</v>
+        <v>0.9326</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6631</v>
+        <v>2.4171</v>
       </c>
       <c r="G14" t="n">
         <v>1.6383</v>
@@ -1546,13 +1546,13 @@
         <v>0.6959</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0754</v>
+        <v>0.7114</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4208</v>
+        <v>0.3029</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6546</v>
+        <v>0.4086</v>
       </c>
       <c r="V14" t="n">
         <v>0.5361</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2251</v>
+        <v>3.1395</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9267</v>
+        <v>2.2806</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2984</v>
+        <v>0.8589</v>
       </c>
       <c r="G15" t="n">
         <v>2.3915</v>
@@ -1624,13 +1624,13 @@
         <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9498</v>
+        <v>-0.0354</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1766</v>
+        <v>0.1772</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7732</v>
+        <v>-0.2126</v>
       </c>
       <c r="V15" t="n">
         <v>-1.0722</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4455</v>
+        <v>0.6407</v>
       </c>
       <c r="E16" t="n">
-        <v>2.466</v>
+        <v>1.5179</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.0205</v>
+        <v>-0.8772</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7277</v>
+        <v>2.132</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9376</v>
+        <v>-1.8964</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7901</v>
+        <v>4.0284</v>
       </c>
       <c r="J16" t="n">
-        <v>4.3944</v>
+        <v>4.1991</v>
       </c>
       <c r="K16" t="n">
-        <v>3.23</v>
+        <v>0.7429</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1643</v>
+        <v>3.4561</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6666</v>
+        <v>-2.067</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.2925</v>
+        <v>-2.6393</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6258</v>
+        <v>0.5723</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.0154</v>
+        <v>-5.3349</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.871</v>
+        <v>-7.1905</v>
       </c>
       <c r="R16" t="n">
         <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>2.0889</v>
+        <v>-0.4452</v>
       </c>
       <c r="T16" t="n">
-        <v>2.4065</v>
+        <v>0.2205</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3176</v>
+        <v>-0.6657</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.3558</v>
+        <v>4.2888</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5361</v>
+        <v>4.2888</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.8919</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.024</v>
+        <v>0.2599</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1767</v>
+        <v>0.4126</v>
       </c>
       <c r="F17" t="n">
         <v>-0.1527</v>
@@ -1780,10 +1780,10 @@
         <v>0.232</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2399</v>
+        <v>-0.004</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2987</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U17" t="n">
         <v>0.0589</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.112</v>
+        <v>-0.4924</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0461</v>
+        <v>1.4044</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1581</v>
+        <v>-1.8968</v>
       </c>
       <c r="G18" t="n">
-        <v>2.132</v>
+        <v>2.7277</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.8964</v>
+        <v>0.9376</v>
       </c>
       <c r="I18" t="n">
-        <v>4.0284</v>
+        <v>1.7901</v>
       </c>
       <c r="J18" t="n">
-        <v>4.1991</v>
+        <v>4.3944</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7429</v>
+        <v>3.23</v>
       </c>
       <c r="L18" t="n">
-        <v>3.4561</v>
+        <v>1.1643</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.067</v>
+        <v>-1.6666</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.6393</v>
+        <v>-2.2925</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5723</v>
+        <v>0.6258</v>
       </c>
       <c r="P18" t="n">
-        <v>-5.3349</v>
+        <v>-3.0154</v>
       </c>
       <c r="Q18" t="n">
-        <v>-7.1905</v>
+        <v>-4.871</v>
       </c>
       <c r="R18" t="n">
         <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.198</v>
+        <v>1.151</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2513</v>
+        <v>1.3449</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9467</v>
+        <v>-0.1939</v>
       </c>
       <c r="V18" t="n">
-        <v>4.2888</v>
+        <v>-1.3558</v>
       </c>
       <c r="W18" t="n">
-        <v>4.2888</v>
+        <v>0.5361</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.8919</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3818</v>
+        <v>-1.7693</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0616</v>
+        <v>-0.4154</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3202</v>
+        <v>-1.3538</v>
       </c>
       <c r="G19" t="n">
         <v>-3.2384</v>
@@ -1936,13 +1936,13 @@
         <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6067</v>
+        <v>0.2192</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1993</v>
+        <v>0.8454</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5926</v>
+        <v>-0.6262</v>
       </c>
       <c r="V19" t="n">
         <v>-0.1418</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>W. HERNANGOMEZ</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8205</v>
+        <v>-1.9507</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4126</v>
+        <v>-2.7931</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4079</v>
+        <v>0.8423</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.4525</v>
+        <v>-0.4598</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.4358</v>
+        <v>0.012</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0167</v>
+        <v>-0.4718</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.5372</v>
+        <v>-0.7527</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.574</v>
+        <v>0.0336</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0368</v>
+        <v>-0.7863</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9153</v>
+        <v>0.293</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8618</v>
+        <v>-0.0216</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0535</v>
+        <v>0.3145</v>
       </c>
       <c r="P20" t="n">
-        <v>0.232</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R20" t="n">
         <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>1.4</v>
+        <v>0.5966</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1246</v>
+        <v>0.2792</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2754</v>
+        <v>0.3174</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.271</v>
+        <v>-2.1778</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1469</v>
+        <v>-2.9543</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8759</v>
+        <v>0.7765</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4598</v>
+        <v>-1.86</v>
       </c>
       <c r="H21" t="n">
-        <v>0.012</v>
+        <v>-1.4284</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4718</v>
+        <v>-0.4316</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7527</v>
+        <v>-2.0739</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0336</v>
+        <v>-0.6484</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7863</v>
+        <v>-1.4255</v>
       </c>
       <c r="M21" t="n">
-        <v>0.293</v>
+        <v>0.2139</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0216</v>
+        <v>-0.78</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3145</v>
+        <v>0.9939</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.0876</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.3195</v>
+        <v>-1.3917</v>
       </c>
       <c r="R21" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2763</v>
+        <v>0.288</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0747</v>
+        <v>0.5113</v>
       </c>
       <c r="U21" t="n">
-        <v>0.351</v>
+        <v>-0.2234</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>W. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3229</v>
+        <v>-2.8421</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4824</v>
+        <v>-2.3562</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1595</v>
+        <v>-0.4859</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.86</v>
+        <v>-3.4525</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.4284</v>
+        <v>-3.4358</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4316</v>
+        <v>-0.0167</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.0739</v>
+        <v>-2.5372</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6484</v>
+        <v>-2.574</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.4255</v>
+        <v>0.0368</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2139</v>
+        <v>-0.9153</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.78</v>
+        <v>-0.8618</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9939</v>
+        <v>-0.0535</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1428</v>
+        <v>0.3785</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9831</v>
+        <v>0.181</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8404</v>
+        <v>0.1975</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.9831</v>
+        <v>-6.1746</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.7292</v>
+        <v>-4.0215</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2539</v>
+        <v>-2.1531</v>
       </c>
       <c r="G23" t="n">
         <v>-4.2669</v>
@@ -2248,13 +2248,13 @@
         <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8606</v>
+        <v>-0.0521</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2987</v>
+        <v>0.409</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5619</v>
+        <v>-0.461</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.926000000000001</v>
+        <v>-2.353500000000002</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7427000000000001</v>
+        <v>0.7425000000000015</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.668699999999999</v>
+        <v>-3.0961</v>
       </c>
       <c r="G24" t="n">
-        <v>0.172200000000001</v>
+        <v>0.1722000000000001</v>
       </c>
       <c r="H24" t="n">
         <v>-10.8692</v>
@@ -2302,13 +2302,13 @@
         <v>10.0445</v>
       </c>
       <c r="K24" t="n">
-        <v>4.223400000000002</v>
+        <v>4.2234</v>
       </c>
       <c r="L24" t="n">
         <v>5.8208</v>
       </c>
       <c r="M24" t="n">
-        <v>-9.872100000000001</v>
+        <v>-9.8721</v>
       </c>
       <c r="N24" t="n">
         <v>-15.0928</v>
@@ -2326,16 +2326,16 @@
         <v>11.5978</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7467000000000001</v>
+        <v>2.319500000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>4.2875</v>
+        <v>4.2874</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.5408</v>
+        <v>-1.9677</v>
       </c>
       <c r="V24" t="n">
-        <v>2.113300000000001</v>
+        <v>2.1133</v>
       </c>
       <c r="W24" t="n">
         <v>4.9667</v>
